--- a/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,71</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 0,0</t>
+          <t>-4,99; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,51</t>
+          <t>-4,79; -0,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 0,0</t>
+          <t>-6,11; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-2,68; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,78</t>
+          <t>-1,32; 0,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,0</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,54</t>
+          <t>-0,18; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,42</t>
+          <t>-0,52; 0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">

--- a/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 7,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,0</t>
+          <t>-4,96; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -0,51</t>
+          <t>-4,69; -0,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,0; 6,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,0</t>
+          <t>-5,65; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,0</t>
+          <t>-2,67; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,78</t>
+          <t>-1,31; 0,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-2,75; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,25</t>
+          <t>-0,72; 0,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,33</t>
+          <t>-0,45; 0,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 199,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">

--- a/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,61</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,0</t>
+          <t>-4,84; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -0,51</t>
+          <t>-4,04; -0,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 5,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,0</t>
+          <t>-5,75; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,0</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,78</t>
+          <t>-1,34; 0,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>-2,68; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,22 +1274,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,24</t>
+          <t>-0,72; 0,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,57</t>
+          <t>-0,18; 0,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,4</t>
+          <t>-0,52; 0,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 199,42</t>
+          <t>-100,0; 217,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">

--- a/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1007-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,139 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.13361294884292</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.072000095519057</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.9860668064202806</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,71</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,45</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,84; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.840332372915272</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.707289834085744</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.448340565440612</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; -0,51</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,54</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>-1.693707688691863</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.119278378496264</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.041414425286789</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.5072646892824977</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>5.535333377144951</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +743,111 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,7</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.151953349320299</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-5,75; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>5.703397508103296</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +855,303 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 0,0</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-8,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 0,78</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-2,68; 0,0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.14083787164464</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-43,56%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>125,36%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-37,02%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="n">
+        <v>-5.752747599526513</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 0,25</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 0,54</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,52; 0,42</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 217,32</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.5346617361428686</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.789066594794794</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-0.03650608807136907</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-0.7712985984910837</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.08551051039562869</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-1.339718508146518</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="n">
+        <v>-2.677135808593171</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.7848537521765043</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-0.1969377427652194</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.1151616450426736</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.09707885997083063</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-0.4355546520901797</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>1.253565207262312</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-0.3701690442146265</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-0.7248496071098467</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.1840716722681373</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.5238224242818464</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.2525067940675566</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.5412927218598942</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.4153952163391517</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>2.173165577796405</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1160,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
